--- a/database/seeders/data/DataBase_Structure.xlsx
+++ b/database/seeders/data/DataBase_Structure.xlsx
@@ -9,22 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="3" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Department" sheetId="13" r:id="rId1"/>
     <sheet name="Text_Box" sheetId="8" r:id="rId2"/>
     <sheet name="Template" sheetId="2" r:id="rId3"/>
     <sheet name="Heading" sheetId="3" r:id="rId4"/>
-    <sheet name="Question" sheetId="4" r:id="rId5"/>
-    <sheet name="Question_NC" sheetId="6" r:id="rId6"/>
-    <sheet name="Criteria" sheetId="7" r:id="rId7"/>
-    <sheet name="Template_Ref" sheetId="5" r:id="rId8"/>
-    <sheet name="Category" sheetId="9" r:id="rId9"/>
-    <sheet name="Sub_Category" sheetId="10" r:id="rId10"/>
+    <sheet name="Sub_Heading" sheetId="10" r:id="rId5"/>
+    <sheet name="Question" sheetId="4" r:id="rId6"/>
+    <sheet name="Question_NC" sheetId="6" r:id="rId7"/>
+    <sheet name="Criteria" sheetId="7" r:id="rId8"/>
+    <sheet name="Template_Ref" sheetId="5" r:id="rId9"/>
+    <sheet name="Category" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Template_Ref!$B$1:$C$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Template_Ref!$B$1:$C$43</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1643,12 +1643,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SubCategory" displayName="SubCategory" ref="A1:C40" totalsRowShown="0">
-  <autoFilter ref="A1:C40"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="subheading_id"/>
-    <tableColumn id="2" name="heading_id"/>
-    <tableColumn id="3" name="name"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Category" displayName="Category" ref="A1:B127" totalsRowShown="0">
+  <autoFilter ref="A1:B127"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="category_id"/>
+    <tableColumn id="2" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1694,6 +1693,18 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SubCategory" displayName="SubCategory" ref="A1:C40" totalsRowShown="0">
+  <autoFilter ref="A1:C40"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="subheading_id"/>
+    <tableColumn id="2" name="heading_id"/>
+    <tableColumn id="3" name="name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Question" displayName="Question" ref="A1:G151" totalsRowShown="0">
   <autoFilter ref="A1:G151"/>
   <tableColumns count="7">
@@ -1709,7 +1720,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Question_NC" displayName="Question_NC" ref="A1:K151" totalsRowShown="0">
   <autoFilter ref="A1:K151"/>
   <tableColumns count="11">
@@ -1729,7 +1740,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="criteria_Table" displayName="criteria_Table" ref="A1:E33" totalsRowShown="0">
   <autoFilter ref="A1:E33"/>
   <tableColumns count="5">
@@ -1743,24 +1754,13 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Template_ref" displayName="Template_ref" ref="A1:C43" totalsRowShown="0">
   <autoFilter ref="A1:C43"/>
   <tableColumns count="3">
     <tableColumn id="1" name="reference_id"/>
     <tableColumn id="2" name="template_code"/>
     <tableColumn id="3" name="reference_code"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Category" displayName="Category" ref="A1:B127" totalsRowShown="0">
-  <autoFilter ref="A1:B127"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="category_id"/>
-    <tableColumn id="2" name="name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2199,452 +2199,1027 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="29.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C1" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="B2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="B3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="B4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="B6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="B7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="B8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="B9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="B10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="B11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="B12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="B13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="B14" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="B15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="B16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="B18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="B19" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="B20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="B21" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="B22" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="B23" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="B24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="B25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="B26" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="B27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="B28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="B29" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="B30" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="B31" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="B32" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="B33" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="B34" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="B35" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="B36" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="B37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38">
-        <v>6</v>
-      </c>
-      <c r="C38" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="B38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39">
-        <v>6</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="B39" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40">
-        <v>6</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B40" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
         <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5094,6 +5669,464 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C40"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="29.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -8592,7 +9625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -13333,7 +14366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -13924,7 +14957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -14419,1037 +15452,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B127"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90">
-        <v>89</v>
-      </c>
-      <c r="B90" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91">
-        <v>90</v>
-      </c>
-      <c r="B91" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92">
-        <v>91</v>
-      </c>
-      <c r="B92" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93">
-        <v>92</v>
-      </c>
-      <c r="B93" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94">
-        <v>93</v>
-      </c>
-      <c r="B94" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95">
-        <v>94</v>
-      </c>
-      <c r="B95" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96">
-        <v>95</v>
-      </c>
-      <c r="B96" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
-        <v>100</v>
-      </c>
-      <c r="B101" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102">
-        <v>101</v>
-      </c>
-      <c r="B102" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104">
-        <v>103</v>
-      </c>
-      <c r="B104" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105">
-        <v>104</v>
-      </c>
-      <c r="B105" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106">
-        <v>105</v>
-      </c>
-      <c r="B106" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107">
-        <v>106</v>
-      </c>
-      <c r="B107" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108">
-        <v>107</v>
-      </c>
-      <c r="B108" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109">
-        <v>108</v>
-      </c>
-      <c r="B109" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122">
-        <v>121</v>
-      </c>
-      <c r="B122" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125">
-        <v>124</v>
-      </c>
-      <c r="B125" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126">
-        <v>125</v>
-      </c>
-      <c r="B126" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127">
-        <v>126</v>
-      </c>
-      <c r="B127" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>